--- a/templates/PRAP_SourceData_Template_v1.8.xlsx
+++ b/templates/PRAP_SourceData_Template_v1.8.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A118"/>
+  <dimension ref="A1:A126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1105,28 +1105,28 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>ADDING A PERMITTED VALUE</t>
+          <t>ASSIGNMENT DATES ARE OPTIONAL</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Insert a row inside that list's block on the Lists sheet, so the block stays contiguous -</t>
+          <t xml:space="preserve">   Leave assign_start_date and assign_end_date BLANK for somebody who is on the project for</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   the dropdowns read a range, not a scattered set of rows. work_scope_type is meant to be</t>
+          <t xml:space="preserve">   the whole of it - which is most people. A blank date means the project's own, so the two</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   extended this way: the three values supplied are a starting point, not a closed set.</t>
+          <t xml:space="preserve">   never fall out of step when the project's dates move.</t>
         </is>
       </c>
     </row>
@@ -1134,193 +1134,241 @@
       <c r="A87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>WORK SCOPE, AND THE EMPTY ROW THAT COVERS EVERY SCOPE</t>
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Fill them in only for a PARTIAL involvement: somebody who joins late, leaves early, or</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   PeriodWeightStandard and RoleFactor are keyed on work_scope_type as well as on the project</t>
+          <t xml:space="preserve">   covers one stretch of a longer study.</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   type, the phase and the period. A row with work_scope_type EMPTY applies to EVERY scope.</t>
-        </is>
-      </c>
+      <c r="A90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr"/>
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>ADDING A PERMITTED VALUE</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   So fill the empty-scope rows first - they are your baseline - and add a scope-specific row</t>
+          <t xml:space="preserve">   Insert a row inside that list's block on the Lists sheet, so the block stays contiguous -</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   only where that scope really does change the number. A project looks for its own scope</t>
+          <t xml:space="preserve">   the dropdowns read a range, not a scattered set of rows. work_scope_type is meant to be</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   first and falls back to the empty row, so nothing has to be entered three times to say</t>
+          <t xml:space="preserve">   extended this way: the three values supplied are a starting point, not a closed set.</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   the same thing three times.</t>
-        </is>
-      </c>
+      <c r="A95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr"/>
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>WORK SCOPE, AND THE EMPTY ROW THAT COVERS EVERY SCOPE</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>BEFORE YOU USE THIS FILE</t>
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   PeriodWeightStandard and RoleFactor are keyed on work_scope_type as well as on the project</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1. Delete the grey example row from every sheet that has one.</t>
+          <t xml:space="preserve">   type, the phase and the period. A row with work_scope_type EMPTY applies to EVERY scope.</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   2. Enter your projects, people and assignments.</t>
-        </is>
-      </c>
+      <c r="A99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   3. Then, when you have seen the figures: review the DEFAULT ASSUMPTIONS.</t>
+          <t xml:space="preserve">   So fill the empty-scope rows first - they are your baseline - and add a scope-specific row</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr"/>
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   only where that scope really does change the number. A project looks for its own scope</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>THE DEFAULT ASSUMPTIONS</t>
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   first and falls back to the empty row, so nothing has to be entered three times to say</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   PeriodWeightStandard (84 rows) and RoleFactor (429 rows) arrive FILLED IN.</t>
+          <t xml:space="preserve">   the same thing three times.</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   They are the same figures the application starts a blank plan with, so the two agree</t>
-        </is>
-      </c>
+      <c r="A104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   from the first day, and they are a STARTING POINT rather than a company standard.</t>
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>BEFORE YOU USE THIS FILE</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr"/>
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   1. Delete the grey example row from every sheet that has one.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   The shape is what to judge first, before any single number: start-up and close-out</t>
+          <t xml:space="preserve">   2. Enter your projects, people and assignments.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   are heavier than conduct; later phases are heavier than earlier ones; a biosimilar</t>
+          <t xml:space="preserve">   3. Then, when you have seen the figures: review the DEFAULT ASSUMPTIONS.</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   trial is lighter than a new-drug trial at the same phase; and each role's burden</t>
-        </is>
-      </c>
+      <c r="A109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   moves across the life of a trial rather than sitting flat.</t>
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>THE DEFAULT ASSUMPTIONS</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr"/>
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   PeriodWeightStandard (84 rows) and RoleFactor (429 rows) arrive FILLED IN.</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Every row says 'Default assumption - replace with your own figure' in its note</t>
+          <t xml:space="preserve">   They are the same figures the application starts a blank plan with, so the two agree</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   column. Replacing a figure is an ordinary edit; the note is there so that a number</t>
+          <t xml:space="preserve">   from the first day, and they are a STARTING POINT rather than a company standard.</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   nobody has reviewed can still be told apart from one somebody chose.</t>
-        </is>
-      </c>
+      <c r="A114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr"/>
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   The shape is what to judge first, before any single number: start-up and close-out</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   work_scope_type is EMPTY on every default row, which means each one applies to every</t>
+          <t xml:space="preserve">   are heavier than conduct; later phases are heavier than earlier ones; a biosimilar</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   scope. Add a row with a scope filled in only where that scope really changes the</t>
+          <t xml:space="preserve">   trial is lighter than a new-drug trial at the same phase; and each role's burden</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   moves across the life of a trial rather than sitting flat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Every row says 'Default assumption - replace with your own figure' in its note</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   column. Replacing a figure is an ordinary edit; the note is there so that a number</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   nobody has reviewed can still be told apart from one somebody chose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   work_scope_type is EMPTY on every default row, which means each one applies to every</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   scope. Add a row with a scope filled in only where that scope really changes the</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">   number - the project will find it first and fall back to the default otherwise.</t>
         </is>
